--- a/data/templates/문제등록_양식.xlsx
+++ b/data/templates/문제등록_양식.xlsx
@@ -34,7 +34,8 @@
     <comment ref="C1" authorId="0">
       <text>
         <r>
-          <t>필수. 채점 근거가 되는 정답/해설 전문. 비우면 채점 기준을 만들 수 없어 출제에서 제외됩니다.</t>
+          <t xml:space="preserve">필수. 채점 근거가 되는 정답/해설 전문. 비우면 채점 기준을 만들 수 없어 출제에서 제외됩니다.
+여러 항목을 적을 때는 셀 안에서 Alt+Enter 로 줄을 바꾸세요. 쉼표·슬래시는 구분자로 쓰지 마세요.</t>
         </r>
       </text>
     </comment>
@@ -92,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
   <si>
     <t>번호</t>
   </si>
@@ -178,7 +179,8 @@
     <t>필수. 문제 발문을 그대로 적습니다. 예) 슬러지 벌킹의 원인을 3가지 서술하시오.</t>
   </si>
   <si>
-    <t>필수. 채점 근거가 되는 정답/해설 전문. 비우면 채점 기준을 만들 수 없어 출제에서 제외됩니다.</t>
+    <t xml:space="preserve">필수. 채점 근거가 되는 정답/해설 전문. 비우면 채점 기준을 만들 수 없어 출제에서 제외됩니다.
+여러 항목을 적을 때는 셀 안에서 Alt+Enter 로 줄을 바꾸세요. 쉼표·슬래시는 구분자로 쓰지 마세요.</t>
   </si>
   <si>
     <t>선택. "3가지 서술" 같은 문제의 3. 비우면 문제 본문에서 자동 인식합니다.</t>
@@ -218,6 +220,24 @@
   </si>
   <si>
     <t xml:space="preserve">  · 비워두면 모범답안을 읽고 AI가 항목을 나눠줍니다.</t>
+  </si>
+  <si>
+    <t>■ 모범답안에 여러 항목을 적을 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 가장 정확한 방법은 항목1~5 열에 하나씩 나눠 적는 것입니다. "5가지" 문제면 항목 열 5개가 딱 맞습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 모범답안 칸에 몰아서 적는다면 셀 안에서 Alt+Enter 로 줄을 바꿔 항목을 나누세요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 줄바꿈 외에 "1. 2. 3.", "①②③", "- " 불릿, 문장 종결(…다.)도 항목 경계로 인식합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 쉼표(,)와 슬래시(/)는 구분자로 쓰지 마세요. "질소, 인 등 영양염류"나 "F/M비"처럼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    항목 내용 안에 자주 들어가는 문자라 멀쩡한 항목이 잘못 잘립니다.</t>
   </si>
   <si>
     <t>■ 주의</t>
@@ -2284,7 +2304,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2481,8 +2501,57 @@
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
     </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="23">
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:C11"/>
@@ -2499,6 +2568,13 @@
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/data/templates/문제등록_양식.xlsx
+++ b/data/templates/문제등록_양식.xlsx
@@ -49,42 +49,45 @@
     <comment ref="E1" authorId="0">
       <text>
         <r>
-          <t>선택. 예) 2023년 1회</t>
+          <t xml:space="preserve">선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다.
+채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.
+항목 앞에 *를 붙이면 필수 항목이 되어 반드시 답안에 있어야 합니다. 예) *정의: 조류가 과다 번식하는 현상</t>
         </r>
       </text>
     </comment>
     <comment ref="F1" authorId="0">
       <text>
         <r>
-          <t>선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다. 채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.</t>
+          <t xml:space="preserve">선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다.
+채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.
+항목 앞에 *를 붙이면 필수 항목이 되어 반드시 답안에 있어야 합니다. 예) *정의: 조류가 과다 번식하는 현상</t>
         </r>
       </text>
     </comment>
     <comment ref="G1" authorId="0">
       <text>
         <r>
-          <t>선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다. 채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.</t>
+          <t xml:space="preserve">선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다.
+채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.
+항목 앞에 *를 붙이면 필수 항목이 되어 반드시 답안에 있어야 합니다. 예) *정의: 조류가 과다 번식하는 현상</t>
         </r>
       </text>
     </comment>
     <comment ref="H1" authorId="0">
       <text>
         <r>
-          <t>선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다. 채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.</t>
+          <t xml:space="preserve">선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다.
+채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.
+항목 앞에 *를 붙이면 필수 항목이 되어 반드시 답안에 있어야 합니다. 예) *정의: 조류가 과다 번식하는 현상</t>
         </r>
       </text>
     </comment>
     <comment ref="I1" authorId="0">
       <text>
         <r>
-          <t>선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다. 채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0">
-      <text>
-        <r>
-          <t>선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다. 채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.</t>
+          <t xml:space="preserve">선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다.
+채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.
+항목 앞에 *를 붙이면 필수 항목이 되어 반드시 답안에 있어야 합니다. 예) *정의: 조류가 과다 번식하는 현상</t>
         </r>
       </text>
     </comment>
@@ -93,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="64">
   <si>
     <t>번호</t>
   </si>
@@ -105,9 +108,6 @@
   </si>
   <si>
     <t>요구항목수</t>
-  </si>
-  <si>
-    <t>연도회차</t>
   </si>
   <si>
     <t>항목1</t>
@@ -137,9 +137,6 @@
 질소·인 등 영양염류의 불균형도 벌킹을 유발한다.</t>
   </si>
   <si>
-    <t>2023년 1회</t>
-  </si>
-  <si>
     <t>사상성 미생물의 과다 증식</t>
   </si>
   <si>
@@ -162,6 +159,34 @@
   </si>
   <si>
     <t>최적 응집제 주입량과 최적 pH를 실험적으로 결정하기 위한 시험이다. 교반 강도와 시간을 달리하며 플록 형성 상태와 상등수 탁도를 관찰해 응집 조건을 도출한다.</t>
+  </si>
+  <si>
+    <t>예시3</t>
+  </si>
+  <si>
+    <t>부영양화의 정의를 쓰고 방지대책을 3가지 서술하시오.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부영양화란 질소·인 등 영양염류가 유입되어 조류가 과다 번식하고 수질이 악화되는 현상이다.
+고도처리로 질소·인을 제거한다.
+무린세제 사용을 확대하고 비점오염원을 관리한다.
+호소 바닥의 저니토를 준설해 내부부하를 제거한다.
+황산동 등 살조제를 살포하거나 폭기해 성층을 파괴한다.</t>
+  </si>
+  <si>
+    <t>*정의: 영양염류 유입으로 조류가 과다 번식해 수질이 악화되는 현상</t>
+  </si>
+  <si>
+    <t>고도처리로 질소·인 제거</t>
+  </si>
+  <si>
+    <t>무린세제 사용과 비점오염원 관리</t>
+  </si>
+  <si>
+    <t>저니토 준설로 내부부하 제거</t>
+  </si>
+  <si>
+    <t>살조제 살포 또는 폭기로 성층 파괴</t>
   </si>
   <si>
     <t>열 제목</t>
@@ -186,13 +211,12 @@
     <t>선택. "3가지 서술" 같은 문제의 3. 비우면 문제 본문에서 자동 인식합니다.</t>
   </si>
   <si>
-    <t>선택. 예) 2023년 1회</t>
-  </si>
-  <si>
     <t>항목1~5</t>
   </si>
   <si>
-    <t>선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다. 채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.</t>
+    <t xml:space="preserve">선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다.
+채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.
+항목 앞에 *를 붙이면 필수 항목이 되어 반드시 답안에 있어야 합니다. 예) *정의: 조류가 과다 번식하는 현상</t>
   </si>
   <si>
     <t>■ 채점 방식</t>
@@ -220,6 +244,27 @@
   </si>
   <si>
     <t xml:space="preserve">  · 비워두면 모범답안을 읽고 AI가 항목을 나눠줍니다.</t>
+  </si>
+  <si>
+    <t>■ 필수 항목 (*) — "정의를 쓰고 대책 3가지" 같은 복합 문제용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 항목 앞에 *를 붙이면 반드시 답안에 있어야 하는 필수 항목이 됩니다. 예) *정의: 조류가 과다 번식하는 현상</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 필수 항목은 맞힌 만큼 그대로 인정되고, 나머지 항목은 (요구항목수 - 필수 개수)개까지만 인정됩니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 예) 요구항목수 4, *정의 1개 + 대책 후보 5개 → 정의는 반드시, 대책은 후보 중 3개면 만점.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        정의를 빼먹고 대책만 5개 써도 3/4 = 4점(부분정답)에 그칩니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 복합 문제는 요구항목수를 직접 적어주세요. 비우면 문제 본문의 "3가지"가 잡혀 정의 몫이 빠집니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 필수 항목이 요구항목수보다 많으면 요구항목수를 필수 개수로 올려서 채점합니다.</t>
   </si>
   <si>
     <t>■ 모범답안에 여러 항목을 적을 때</t>
@@ -293,12 +338,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2563EB"/>
+        <fgColor rgb="FF64748B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF64748B"/>
+        <fgColor rgb="FF2563EB"/>
       </patternFill>
     </fill>
     <fill>
@@ -688,1614 +733,1633 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J303"/>
+  <dimension ref="A1:I304"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="3" width="52" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="10" width="30" customWidth="1"/>
+    <col min="5" max="9" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+    </row>
+    <row r="2" ht="92" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" ht="92" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="D2" s="3">
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="3" t="s">
+    </row>
+    <row r="3" ht="92" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" ht="92" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="92" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>1</v>
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="3">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="4">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" s="4">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" s="4">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" s="4">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" s="4">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" s="4">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" s="4">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" s="4">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" s="4">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" s="4">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" s="4">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" s="4">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" s="4">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274" s="4">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" s="4">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" s="4">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" s="4">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" s="4">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279" s="4">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280" s="4">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" s="4">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282" s="4">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283" s="4">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" s="4">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285" s="4">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" s="4">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287" s="4">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" s="4">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289" s="4">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" s="4">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291" s="4">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292" s="4">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" s="4">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294" s="4">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295" s="4">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296" s="4">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" s="4">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" s="4">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299" s="4">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300" s="4">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301" s="4">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302" s="4">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304" s="4">
         <v>300</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
@@ -2304,7 +2368,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2314,13 +2378,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2328,10 +2392,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2339,10 +2403,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2350,10 +2414,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2361,197 +2425,243 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
+      <c r="A9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
+      <c r="A14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
+      <c r="A15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
+      <c r="A19" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
+      <c r="A20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
     </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="31">
+    <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:C11"/>
@@ -2575,6 +2685,13 @@
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A38:C38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/data/templates/문제등록_양식.xlsx
+++ b/data/templates/문제등록_양식.xlsx
@@ -91,12 +91,39 @@
         </r>
       </text>
     </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다.
+채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.
+항목 앞에 *를 붙이면 필수 항목이 되어 반드시 답안에 있어야 합니다. 예) *정의: 조류가 과다 번식하는 현상</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다.
+채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.
+항목 앞에 *를 붙이면 필수 항목이 되어 반드시 답안에 있어야 합니다. 예) *정의: 조류가 과다 번식하는 현상</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다.
+채우면 이 항목들이 그대로 채점 기준이 되고, 비우면 모범답안에서 AI가 자동 추출합니다.
+항목 앞에 *를 붙이면 필수 항목이 되어 반드시 답안에 있어야 합니다. 예) *정의: 조류가 과다 번식하는 현상</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="79">
   <si>
     <t>번호</t>
   </si>
@@ -123,6 +150,15 @@
   </si>
   <si>
     <t>항목5</t>
+  </si>
+  <si>
+    <t>항목6</t>
+  </si>
+  <si>
+    <t>항목7</t>
+  </si>
+  <si>
+    <t>항목8</t>
   </si>
   <si>
     <t>예시1</t>
@@ -189,6 +225,42 @@
     <t>살조제 살포 또는 폭기로 성층 파괴</t>
   </si>
   <si>
+    <t>예시4</t>
+  </si>
+  <si>
+    <t>전기집진기 운전 시 분진의 비저항이 10^4 Ω·cm 이하일 때와 10^11 Ω·cm 이상일 때의 발생현상과 방지책을 각각 쓰시오.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">비저항이 낮으면 집진극에서 전하를 잃은 분진이 다시 날리는 재비산이 일어난다.
+NH3를 투입하고, 습도를 조절하며, 처리가스 속도를 낮춘다.
+비저항이 높으면 분진층에서 역방향 방전이 일어나는 역전리가 발생한다.
+SO3를 투입하고, 습도를 조절하며, 전극을 청결하게 유지한다.</t>
+  </si>
+  <si>
+    <t>*저비저항: 재비산 발생</t>
+  </si>
+  <si>
+    <t>NH3(암모니아) 투입</t>
+  </si>
+  <si>
+    <t>가스 증습으로 습도 조절</t>
+  </si>
+  <si>
+    <t>처리가스 속도 낮춤</t>
+  </si>
+  <si>
+    <t>*고비저항: 역전리 발생</t>
+  </si>
+  <si>
+    <t>SO3 투입</t>
+  </si>
+  <si>
+    <t>탈진 주기 단축</t>
+  </si>
+  <si>
+    <t>전극 청결 유지</t>
+  </si>
+  <si>
     <t>열 제목</t>
   </si>
   <si>
@@ -211,7 +283,7 @@
     <t>선택. "3가지 서술" 같은 문제의 3. 비우면 문제 본문에서 자동 인식합니다.</t>
   </si>
   <si>
-    <t>항목1~5</t>
+    <t>항목1~8</t>
   </si>
   <si>
     <t xml:space="preserve">선택. "n가지" 문제에서 정답으로 인정할 항목을 하나씩 나눠 적습니다.
@@ -270,7 +342,10 @@
     <t>■ 모범답안에 여러 항목을 적을 때</t>
   </si>
   <si>
-    <t xml:space="preserve">  · 가장 정확한 방법은 항목1~5 열에 하나씩 나눠 적는 것입니다. "5가지" 문제면 항목 열 5개가 딱 맞습니다.</t>
+    <t xml:space="preserve">  · 가장 정확한 방법은 항목 열에 하나씩 나눠 적는 것입니다. "5가지" 문제면 항목 5칸을 쓰면 됩니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 항목 열은 8개까지 있습니다. 정의와 대책이 섞인 복합 문제도 한 행에 담을 수 있습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">  · 모범답안 칸에 몰아서 적는다면 셀 안에서 Alt+Enter 로 줄을 바꿔 항목을 나누세요.</t>
@@ -733,16 +808,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I304"/>
+  <dimension ref="A1:L305"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="3" width="52" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="9" width="30" customWidth="1"/>
+    <col min="5" max="12" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -770,1596 +845,1670 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" ht="92" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" ht="92" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3">
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" ht="92" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" ht="92" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="92" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="92" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
         <v>4</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="3">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="4">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" s="4">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" s="4">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" s="4">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" s="4">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" s="4">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" s="4">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" s="4">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" s="4">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" s="4">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" s="4">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" s="4">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" s="4">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274" s="4">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" s="4">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" s="4">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" s="4">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" s="4">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279" s="4">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280" s="4">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" s="4">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282" s="4">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283" s="4">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" s="4">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285" s="4">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" s="4">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287" s="4">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" s="4">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289" s="4">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" s="4">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291" s="4">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292" s="4">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" s="4">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294" s="4">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295" s="4">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296" s="4">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" s="4">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" s="4">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299" s="4">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300" s="4">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301" s="4">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302" s="4">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304" s="4">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305" s="4">
         <v>300</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:L1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
@@ -2368,7 +2517,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2378,13 +2527,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2392,10 +2541,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2403,10 +2552,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2414,10 +2563,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2425,242 +2574,249 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
+      <c r="A34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
+      <c r="A35" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
     </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A10:C10"/>
@@ -2692,6 +2848,7 @@
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A39:C39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
